--- a/data/trans_orig/IP28_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP28_R-Habitat-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5232</t>
+          <t>5159</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>764</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>6978</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>132561</t>
+          <t>132302</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>146511</t>
+          <t>146584</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>282468</t>
+          <t>281440</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>287773</t>
+          <t>287654</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7092</t>
+          <t>7152</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7149</t>
+          <t>7044</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3327</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11922</t>
+          <t>11313</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>186114</t>
+          <t>186054</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>191924</t>
+          <t>191915</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>201078</t>
+          <t>201183</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>207042</t>
+          <t>206923</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>389511</t>
+          <t>390120</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>398106</t>
+          <t>398168</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>3844</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>653</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7325</t>
+          <t>6723</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7844</t>
+          <t>7436</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>132110</t>
+          <t>131837</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141849</t>
+          <t>142451</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>148449</t>
+          <t>148521</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>277011</t>
+          <t>277419</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>283480</t>
+          <t>283498</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>779</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7897</t>
+          <t>8032</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>4731</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1761</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10257</t>
+          <t>9647</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>197054</t>
+          <t>196919</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>204169</t>
+          <t>204172</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>201711</t>
+          <t>201742</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>401168</t>
+          <t>401778</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>409664</t>
+          <t>409658</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>4925</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15464</t>
+          <t>14519</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4886</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14804</t>
+          <t>14795</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11499</t>
+          <t>11918</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25294</t>
+          <t>25424</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>655049</t>
+          <t>655994</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>665664</t>
+          <t>665588</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>700814</t>
+          <t>700823</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>710926</t>
+          <t>710732</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1360837</t>
+          <t>1360707</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1374632</t>
+          <t>1374213</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>737</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7168</t>
+          <t>6761</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>723</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7684</t>
+          <t>7410</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2755</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11070</t>
+          <t>11629</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>118230</t>
+          <t>118637</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>124640</t>
+          <t>124661</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>133935</t>
+          <t>134209</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>140881</t>
+          <t>140896</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>255947</t>
+          <t>255388</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>264262</t>
+          <t>264205</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3765</t>
+          <t>3720</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7881</t>
+          <t>8348</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>1930</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>8581</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>178770</t>
+          <t>178815</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>195779</t>
+          <t>195312</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>202298</t>
+          <t>202330</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>377324</t>
+          <t>377614</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>384304</t>
+          <t>384265</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>589</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>5514</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>3634</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>1194</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>136819</t>
+          <t>137094</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>142015</t>
+          <t>142019</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>147342</t>
+          <t>147996</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>287382</t>
+          <t>287117</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>293014</t>
+          <t>293044</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>3783</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12790</t>
+          <t>13441</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7162</t>
+          <t>7289</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6280</t>
+          <t>6699</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17009</t>
+          <t>17712</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>183026</t>
+          <t>182375</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>192075</t>
+          <t>192033</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>185258</t>
+          <t>185131</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>191165</t>
+          <t>191164</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>371227</t>
+          <t>370524</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>381956</t>
+          <t>381537</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7527</t>
+          <t>8273</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20054</t>
+          <t>19521</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6807</t>
+          <t>6996</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17821</t>
+          <t>18066</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17707</t>
+          <t>17071</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33627</t>
+          <t>33683</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>626303</t>
+          <t>626836</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>638830</t>
+          <t>638084</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>671509</t>
+          <t>671264</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>682523</t>
+          <t>682334</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1302059</t>
+          <t>1302003</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1317979</t>
+          <t>1318615</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>5333</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>679</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6369</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>118060</t>
+          <t>117393</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>124597</t>
+          <t>124336</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>244163</t>
+          <t>244938</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>249845</t>
+          <t>249853</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>572</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4881</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7990</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>181121</t>
+          <t>180562</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>184874</t>
+          <t>184871</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>190279</t>
+          <t>190937</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>373574</t>
+          <t>374075</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>380293</t>
+          <t>380298</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3844</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>622</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>6777</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>138727</t>
+          <t>138954</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>150352</t>
+          <t>150288</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>155061</t>
+          <t>155066</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>291179</t>
+          <t>291482</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>297099</t>
+          <t>297109</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>701</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>6848</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>4534</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8943</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>177226</t>
+          <t>177498</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>183651</t>
+          <t>183645</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>181929</t>
+          <t>181385</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>361322</t>
+          <t>361396</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>368863</t>
+          <t>368862</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3196</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11478</t>
+          <t>11189</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11437</t>
+          <t>11672</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19699</t>
+          <t>20111</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>621744</t>
+          <t>622033</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>630026</t>
+          <t>630001</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>655961</t>
+          <t>655726</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>664147</t>
+          <t>664136</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1280921</t>
+          <t>1280509</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1292547</t>
+          <t>1292470</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>503</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5369</t>
+          <t>4325</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8165</t>
+          <t>8188</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>109928</t>
+          <t>109590</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>116063</t>
+          <t>116050</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>135043</t>
+          <t>136087</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>248801</t>
+          <t>248778</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>255839</t>
+          <t>255903</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>706</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6761</t>
+          <t>6704</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>694</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6595</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>246237</t>
+          <t>246294</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>252256</t>
+          <t>252292</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>436133</t>
+          <t>436282</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>442038</t>
+          <t>442034</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10214</t>
+          <t>9600</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>489</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6857</t>
+          <t>6993</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>2888</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12805</t>
+          <t>12701</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>179371</t>
+          <t>179985</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>188243</t>
+          <t>188223</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>177621</t>
+          <t>177485</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>184007</t>
+          <t>183989</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>361258</t>
+          <t>361362</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>371112</t>
+          <t>371175</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>825</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7440</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5086</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7658,42 +7658,42 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>4191</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>1679</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>9801</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>2,82%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>4191</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>1584</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>9779</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>159332</t>
+          <t>158756</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>165982</t>
+          <t>165947</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>175566</t>
+          <t>176328</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7766,47 +7766,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>97,61%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>343233</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>337623</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>345745</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>98,79%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>97,18%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>470</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>343233</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>337645</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>345840</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>98,79%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>97,19%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17119</t>
+          <t>16868</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>3723</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13771</t>
+          <t>13517</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>10463</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25233</t>
+          <t>25992</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>645521</t>
+          <t>645772</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>657450</t>
+          <t>657626</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>744770</t>
+          <t>745024</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>754838</t>
+          <t>754818</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1395948</t>
+          <t>1395189</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1410273</t>
+          <t>1410718</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP28_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP28_R-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -728,67 +728,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>1436</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4809</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,17%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>1245</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4372</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3845</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,2%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1436</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5159</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>638</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>6772</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -836,74 +836,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>150307</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>146934</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>151743</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,05%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96,83%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>135429</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>132302</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>132829</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>136674</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,09%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,8%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,19%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>150307</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>146584</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>151743</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,05%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>96,6%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>420</t>
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>281440</t>
+          <t>281646</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>287654</t>
+          <t>287780</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>151743</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>151743</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>151743</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>136674</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>136674</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>136674</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>151743</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>151743</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>151743</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1071,67 +1071,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>3293</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1190</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7299</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,51%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>3258</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1291</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7152</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7503</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,69%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,67%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3293</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1304</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7044</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>3281</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11313</t>
+          <t>11239</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -1179,74 +1179,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>204934</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>200928</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>207037</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,42%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,49%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,43%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>304</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>189948</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>186054</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>191915</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>185703</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>191911</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,31%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,3%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>96,12%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>99,33%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>204934</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>201183</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>206923</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,42%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>96,62%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,37%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>615</t>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>390120</t>
+          <t>390194</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>398168</t>
+          <t>398152</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>208227</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>208227</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>208227</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>309</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>193206</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>193206</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>193206</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>208227</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>208227</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>208227</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2732</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6753</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,53%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1053</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3844</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4150</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,78%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2732</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>653</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6723</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1357</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7436</t>
+          <t>8078</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -1522,74 +1522,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>146442</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>142421</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>148456</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,17%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,47%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,52%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>134628</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>131837</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>131531</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>135681</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,22%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,17%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>96,94%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>146442</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>142451</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>148521</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,17%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>95,49%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>450</t>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>277419</t>
+          <t>276777</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>283498</t>
+          <t>283513</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149174</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149174</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149174</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>135681</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>135681</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>135681</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149174</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149174</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149174</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,107 +1752,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1350</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4598</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3276</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>779</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8032</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>988</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8211</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,6%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>4,01%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>4626</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>1558</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>9535</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1350</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4731</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>4626</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>1767</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>9647</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -1865,107 +1865,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>205123</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>201875</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>206473</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,35%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,77%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>201675</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>196919</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>204172</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>196740</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>203963</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,4%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,08%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>95,99%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>99,52%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>566</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>406799</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>401890</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>409867</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>98,88%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>97,68%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
         <is>
           <t>99,62%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>205123</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>201742</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>206473</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,35%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,71%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>566</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>406799</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>401778</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>409658</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>98,88%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>97,66%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206473</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206473</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206473</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>268</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>204951</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>204951</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>204951</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206473</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206473</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206473</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2100,69 +2100,69 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>8810</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4679</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>14251</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>8832</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4925</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>14519</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>4603</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>14566</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,32%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>2,17%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>8810</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>4886</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>14795</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>26</t>
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11918</t>
+          <t>11480</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25424</t>
+          <t>25050</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>706808</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>701367</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>710939</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,77%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,01%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,35%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>989</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>661681</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>655994</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>665588</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>655947</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>665910</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,68%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>97,83%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,27%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>706808</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>700823</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>710732</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,77%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>97,93%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1360707</t>
+          <t>1361081</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1374213</t>
+          <t>1374651</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1075</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>715618</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>715618</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>715618</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1002</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>670513</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>670513</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>670513</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1075</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>715618</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>715618</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>715618</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2675,67 +2675,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7359</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,2%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>2821</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>737</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6761</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7289</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,25%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3103</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>723</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7410</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11629</t>
+          <t>11209</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>138516</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>134260</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>140872</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,81%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>94,8%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,47%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>122577</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>118637</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>124661</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>118109</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>124679</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,75%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>94,61%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,41%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>138516</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>134209</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>140896</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,81%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>255388</t>
+          <t>255808</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>264205</t>
+          <t>264229</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>141619</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>141619</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>141619</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>125398</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>125398</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>125398</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>141619</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>141619</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>141619</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3850</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1343</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7741</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>665</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3720</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3073</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3850</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1330</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8348</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>8538</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -3126,74 +3126,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>199810</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>195919</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>202317</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,11%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,2%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,34%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>181870</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>178815</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>179462</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>182535</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,64%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,96%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,32%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>199810</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>195312</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>202330</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,11%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>95,9%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,35%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>570</t>
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>377614</t>
+          <t>377657</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>384265</t>
+          <t>384296</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>203660</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>203660</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>203660</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>282</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>182535</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>182535</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>182535</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>295</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>203660</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>203660</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>203660</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,107 +3356,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3594</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1969</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>589</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5514</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5920</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,38%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>4,15%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>3157</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>1196</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>7349</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,87%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1187</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3634</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>3157</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>1194</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>7121</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>150443</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>148036</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>151630</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,22%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,63%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>140639</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>137094</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>142019</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>136688</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>142011</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,62%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>96,13%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>150443</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>147996</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>151630</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,22%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>287117</t>
+          <t>286889</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>293044</t>
+          <t>293042</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>151630</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>151630</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>151630</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>142608</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>142608</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>142608</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>151630</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>151630</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>151630</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,107 +3699,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3278</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1242</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7205</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>7596</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3783</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>13441</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3866</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>13401</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,88%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,86%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3278</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1256</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7289</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>6,84%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>10875</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>6604</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>17740</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>1,7%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>10875</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>6699</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>17712</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -3812,107 +3812,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>189142</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>185215</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>191178</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,3%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,26%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,35%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>188220</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>182375</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>192033</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>182415</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>191950</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,12%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,14%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,07%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>189142</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>185131</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>191164</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>93,16%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>98,03%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>377361</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>370496</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>381632</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>97,2%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>95,43%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
         <is>
           <t>98,3%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>96,21%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,35%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>504</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>377361</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>370524</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>381537</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>97,2%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>95,44%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>192420</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>192420</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>192420</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>195816</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>195816</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>195816</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>192420</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>192420</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>192420</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11419</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6709</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>18126</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>13052</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>8273</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>19521</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>7493</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>19592</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,02%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>11419</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>6996</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>18066</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17071</t>
+          <t>17910</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33683</t>
+          <t>34532</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>968</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>677911</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>671204</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>682621</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,34%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,37%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,03%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>633305</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>626836</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>638084</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>626765</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>638864</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>97,98%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,98%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,72%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>968</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>677911</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>671264</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>682334</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,34%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1302003</t>
+          <t>1301154</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1318615</t>
+          <t>1317776</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>689330</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>689330</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>689330</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>932</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>646357</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>646357</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>646357</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>985</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>689330</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>689330</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>689330</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1441</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5037</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,88%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>687</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3470</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3526</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,57%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1441</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5333</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>686</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5594</t>
+          <t>5944</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -4730,74 +4730,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>128228</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>124632</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>129669</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,89%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96,12%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>120176</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>117393</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>117337</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>120863</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,43%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>97,13%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,08%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>128228</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>124336</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>129669</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,89%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>95,89%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>336</t>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>244938</t>
+          <t>244588</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>249853</t>
+          <t>249846</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>129669</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>129669</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>129669</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>120863</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>120863</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>120863</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>129669</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>129669</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>129669</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4965,67 +4965,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>1941</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5556</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,83%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>1807</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>572</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4881</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5179</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,97%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1941</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5185</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7489</t>
+          <t>7392</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -5073,74 +5073,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>194181</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>190566</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>195499</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,01%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,17%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,68%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>296</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>183636</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>180562</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>184871</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>180264</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>184872</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,03%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,37%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,21%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>99,69%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>194181</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>190937</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>195500</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,01%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,36%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>583</t>
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>374075</t>
+          <t>374172</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>380298</t>
+          <t>380303</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>196122</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>196122</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>196122</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>299</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>185443</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>185443</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>185443</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>196122</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>196122</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>196122</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,107 +5303,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5221</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1094</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3617</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4408</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,77%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5400</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>3,09%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>3073</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>1189</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>7041</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>3073</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>1150</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>6777</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -5416,107 +5416,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>153710</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>150467</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>155064</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,73%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,65%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,6%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>141477</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>138954</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>138163</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>142571</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,23%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,46%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>96,91%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>153710</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>150288</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>155066</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,73%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,53%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>295186</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>291218</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>297070</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>98,97%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>97,64%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
         <is>
           <t>99,6%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>463</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>295186</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>291482</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>297109</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>98,97%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>97,73%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>155688</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>155688</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>155688</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>142571</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>142571</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>142571</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>155688</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>155688</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>155688</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4535</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2784</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>701</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6848</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6368</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,51%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4534</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>1386</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>8968</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -5759,74 +5759,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>184618</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>181384</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>185919</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,3%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,56%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>181562</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>177498</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>183645</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>177978</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>183638</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,49%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,28%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>96,55%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,62%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>184618</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>181385</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>185919</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,3%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,56%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>505</t>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>361396</t>
+          <t>361297</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>368862</t>
+          <t>368879</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>185919</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>185919</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>185919</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>250</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>184346</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>184346</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>184346</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>185919</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>185919</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>185919</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5994,97 +5994,97 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>6661</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3878</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>11530</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>6372</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3221</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>11189</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>3113</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>11453</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,01%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>6661</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>3262</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>11672</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>13033</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>8009</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>20213</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>1,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>13033</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>8150</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>20111</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6102,99 +6102,99 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>943</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>660737</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>655868</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>663520</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,27%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,42%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>944</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>626850</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>622033</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>630001</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>621769</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>630109</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,99%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>98,23%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,49%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>943</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>660737</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>655726</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>664136</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>98,19%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>99,51%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1887</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1287587</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1280407</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1292611</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>99,0%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,25%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,51%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1887</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1287587</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1280509</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1292470</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>99,0%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
           <t>98,45%</t>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>667398</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>667398</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>667398</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>954</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>633222</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>633222</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>633222</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>953</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>667398</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>667398</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>667398</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1257</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,42%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2388</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>503</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6963</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,05%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,97%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>2510</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>454</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4325</t>
+          <t>7016</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3697</t>
+          <t>3767</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8188</t>
+          <t>8805</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>124649</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>121602</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96,58%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>114165</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>109590</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>116050</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>97,95%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>94,03%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,57%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>139103</t>
+          <t>117728</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>136087</t>
+          <t>113222</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>119784</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>253269</t>
+          <t>242377</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>248778</t>
+          <t>237339</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>255903</t>
+          <t>245036</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>116553</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>116553</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>116553</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>120238</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>120238</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>120238</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>256966</t>
+          <t>246144</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>256966</t>
+          <t>246144</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>256966</t>
+          <t>246144</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,107 +6907,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2354</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6889</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2429</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>706</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6704</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>610</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -7020,74 +7020,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>232850</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>228315</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>234589</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,07%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,74%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>189729</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>183596</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>250569</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>246294</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>252292</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,04%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,35%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>616</t>
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>440299</t>
+          <t>416446</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>436282</t>
+          <t>412553</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>442034</t>
+          <t>418190</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>235204</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>235204</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>235204</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>189729</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>189729</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>189729</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>252998</t>
+          <t>183596</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>252998</t>
+          <t>183596</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>252998</t>
+          <t>183596</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>442728</t>
+          <t>418800</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>442728</t>
+          <t>418800</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>442728</t>
+          <t>418800</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2289</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6988</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,17%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4360</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1362</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9600</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,06%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>4554</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6993</t>
+          <t>10626</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>6677</t>
+          <t>6843</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2888</t>
+          <t>3092</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12701</t>
+          <t>12806</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>185225</t>
+          <t>165146</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>179985</t>
+          <t>160447</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>188223</t>
+          <t>166997</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>182161</t>
+          <t>151650</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>177485</t>
+          <t>145578</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>183989</t>
+          <t>154359</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>367386</t>
+          <t>316796</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>361362</t>
+          <t>310833</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>371175</t>
+          <t>320547</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>167435</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>167435</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>167435</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>184478</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>184478</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>184478</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>374063</t>
+          <t>323639</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>374063</t>
+          <t>323639</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>374063</t>
+          <t>323639</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1132</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3886</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2794</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8016</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3170</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8087</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,49%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,81%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1397</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4324</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4191</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1679</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9801</t>
+          <t>9100</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -7711,69 +7711,69 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>163978</t>
+          <t>167603</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>158756</t>
+          <t>164849</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>165947</t>
+          <t>168735</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>162759</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>157842</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>165119</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>98,09%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>95,13%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>99,51%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>179255</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>176328</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>180652</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,61%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>470</t>
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>343233</t>
+          <t>330361</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>337623</t>
+          <t>325564</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>345745</t>
+          <t>333225</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>168735</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>168735</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>168735</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>166772</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>166772</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>166772</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>180652</t>
+          <t>165929</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>180652</t>
+          <t>165929</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>180652</t>
+          <t>165929</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>347424</t>
+          <t>334664</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>347424</t>
+          <t>334664</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>347424</t>
+          <t>334664</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7033</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3633</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>12623</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>9542</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5014</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>16868</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7453</t>
+          <t>10234</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3723</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13517</t>
+          <t>17750</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>16995</t>
+          <t>17268</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10463</t>
+          <t>10858</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25992</t>
+          <t>26537</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>962</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>690247</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>684657</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>693647</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,99%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,19%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,48%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>927</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>653098</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>645772</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>657626</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>98,56%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,45%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,24%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>962</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>751088</t>
+          <t>615732</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>745024</t>
+          <t>608216</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>754818</t>
+          <t>620721</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1404186</t>
+          <t>1305978</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1395189</t>
+          <t>1296709</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1410718</t>
+          <t>1312388</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>972</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>697280</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>697280</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>697280</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>939</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>662640</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>662640</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>662640</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>972</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>758541</t>
+          <t>625966</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>758541</t>
+          <t>625966</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>758541</t>
+          <t>625966</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1421181</t>
+          <t>1323246</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1421181</t>
+          <t>1323246</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1421181</t>
+          <t>1323246</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
